--- a/reports/devops-juniors-israel-2026-W36.xlsx
+++ b/reports/devops-juniors-israel-2026-W36.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-31T13:33:07</t>
+    <t xml:space="preserve">2026-09-01T11:34:52</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -145,271 +145,580 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMIT Offshore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-systems-engineer-at-commit-offshore-4455869432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior NOC Engineer | Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-noc-engineer-student-position-at-log-on-software-4458883696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist 243285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-243285-at-experis-israel-4458881880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
     <t xml:space="preserve">SAP</t>
   </si>
   <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud System Administrator – AWS/GCP (25559)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
   </si>
   <si>
     <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, GCP, Cloud (any), Networking, Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-system-administrator-%E2%80%93-aws-gcp-25559-at-yael-group-4457268524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8759588002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-moveo-source-4457448532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TECEZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-teceze-4458365687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
     <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
@@ -418,313 +727,52 @@
     <t xml:space="preserve">Oracle</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441086540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-youcc-technologies-ltd-4459214418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ML-Ops Analyst - (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8759593002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior NOC Engineer | Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-noc-engineer-student-position-at-log-on-software-4458883696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-kaltura-4460895402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-at-tata-consultancy-services-4449360209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
@@ -733,22 +781,37 @@
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Kubernetes</t>
@@ -757,30 +820,6 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -809,9 +848,6 @@
   </si>
   <si>
     <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
   <si>
     <t xml:space="preserve">remoteok</t>
@@ -939,7 +975,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -947,7 +983,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1045,7 +1081,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1053,7 +1089,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1061,7 +1097,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1095,7 +1131,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1103,7 +1139,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1114,8 +1150,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1171,7 +1207,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1296,25 +1332,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>61</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3">
-        <v>68</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1322,19 +1358,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>75</v>
@@ -1360,7 +1396,7 @@
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1395,10 +1431,10 @@
         <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>86</v>
@@ -1459,7 +1495,7 @@
         <v>97</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
         <v>44</v>
@@ -1468,13 +1504,13 @@
         <v>98</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -1491,10 +1527,10 @@
         <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>103</v>
@@ -1506,7 +1542,7 @@
         <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1514,10 +1550,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>57</v>
@@ -1526,19 +1562,19 @@
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
@@ -1546,31 +1582,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -1578,13 +1614,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
@@ -1593,16 +1629,16 @@
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -1610,31 +1646,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17">
@@ -1642,19 +1678,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>126</v>
@@ -1666,7 +1702,7 @@
         <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18">
@@ -1674,31 +1710,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1706,31 +1742,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
@@ -1738,31 +1774,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3">
+        <v>20</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="3">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21">
@@ -1770,31 +1806,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="22">
@@ -1802,16 +1838,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
         <v>17</v>
@@ -1820,13 +1856,13 @@
         <v>148</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
@@ -1834,13 +1870,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1849,16 +1885,16 @@
         <v>17</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24">
@@ -1866,31 +1902,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>17</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3">
-        <v>13</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25">
@@ -1898,31 +1934,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
         <v>13</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="26">
@@ -1930,31 +1966,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>13</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="3">
-        <v>12</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1993,7 +2029,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2051,7 +2087,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2072,7 +2108,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2107,7 +2143,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -2142,7 +2178,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2177,7 +2213,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -2188,16 +2224,16 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>61</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3">
-        <v>68</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>176</v>
@@ -2206,30 +2242,30 @@
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K6" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>75</v>
@@ -2247,7 +2283,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -2258,7 +2294,7 @@
         <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
@@ -2282,7 +2318,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2296,10 +2332,10 @@
         <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>86</v>
@@ -2317,7 +2353,7 @@
         <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -2352,7 +2388,7 @@
         <v>94</v>
       </c>
       <c r="K10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2366,7 +2402,7 @@
         <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
         <v>44</v>
@@ -2378,13 +2414,13 @@
         <v>176</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -2401,10 +2437,10 @@
         <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>103</v>
@@ -2419,18 +2455,18 @@
         <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>57</v>
@@ -2439,10 +2475,10 @@
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>176</v>
@@ -2451,33 +2487,33 @@
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>176</v>
@@ -2486,24 +2522,24 @@
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>115</v>
       </c>
       <c r="K14" s="3">
-        <v>11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
@@ -2512,7 +2548,7 @@
         <v>28</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>176</v>
@@ -2521,33 +2557,33 @@
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>176</v>
@@ -2556,30 +2592,30 @@
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="K16" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>126</v>
@@ -2594,30 +2630,30 @@
         <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="K17" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>176</v>
@@ -2626,33 +2662,33 @@
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K18" s="3">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>176</v>
@@ -2661,33 +2697,33 @@
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="K19" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3">
+        <v>20</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="3">
-        <v>23</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>176</v>
@@ -2696,33 +2732,33 @@
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>176</v>
@@ -2731,27 +2767,27 @@
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="K21" s="3">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
         <v>17</v>
@@ -2763,27 +2799,27 @@
         <v>176</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2792,7 +2828,7 @@
         <v>17</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>176</v>
@@ -2801,103 +2837,103 @@
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K23" s="3">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="3">
-        <v>13</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="K24" s="3">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
         <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="K25" s="3">
-        <v>12</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>13</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="3">
-        <v>12</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>176</v>
@@ -2906,24 +2942,24 @@
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
@@ -2932,7 +2968,7 @@
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>176</v>
@@ -2941,59 +2977,59 @@
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="K27" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>12</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>10</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="K28" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3002,39 +3038,39 @@
         <v>10</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>190</v>
@@ -3049,10 +3085,10 @@
         <v>191</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="K30" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3063,13 +3099,13 @@
         <v>193</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E31" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>194</v>
@@ -3084,30 +3120,30 @@
         <v>195</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>196</v>
+        <v>94</v>
       </c>
       <c r="K31" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>197</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="3">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>6</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>176</v>
@@ -3116,68 +3152,68 @@
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K32" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>63</v>
+        <v>202</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="K33" s="3">
-        <v>60</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>176</v>
@@ -3186,33 +3222,33 @@
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="K34" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>176</v>
@@ -3221,33 +3257,33 @@
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="K35" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>176</v>
@@ -3256,85 +3292,223 @@
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K36" s="3">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>219</v>
+        <v>62</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="K37" s="3">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>224</v>
+        <v>45</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E38" s="3">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K38" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>3</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="K39" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>3</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="K40" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="K38" s="3">
-        <v>33</v>
+      <c r="I41" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K41" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K42" s="3">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K38"/>
+  <autoFilter ref="A1:K42"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3373,6 +3547,10 @@
     <hyperlink ref="I36" r:id="rId35"/>
     <hyperlink ref="I37" r:id="rId36"/>
     <hyperlink ref="I38" r:id="rId37"/>
+    <hyperlink ref="I39" r:id="rId38"/>
+    <hyperlink ref="I40" r:id="rId39"/>
+    <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3380,9 +3558,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3414,25 +3592,25 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -3443,7 +3621,7 @@
         <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
         <v>44</v>
@@ -3455,134 +3633,86 @@
         <v>99</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="3">
-        <v>12</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>10</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3597,178 +3727,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>202</v>
+        <v>246</v>
       </c>
       <c r="B5" s="3">
         <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>159</v>
+        <v>248</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B9" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="B11" s="3">
         <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B12" s="3">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -3788,10 +3918,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2">
@@ -3799,10 +3929,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3">
@@ -3810,10 +3940,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4">
@@ -3821,10 +3951,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5">
@@ -3835,7 +3965,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6">
@@ -3846,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -3867,13 +3997,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2">
@@ -3881,10 +4011,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3893,22 +4023,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W36.xlsx
+++ b/reports/devops-juniors-israel-2026-W36.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01T11:34:52</t>
+    <t xml:space="preserve">2026-09-02T11:10:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -145,6 +145,39 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -169,9 +202,6 @@
     <t xml:space="preserve">Paragon</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -181,513 +211,528 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMMIT Offshore</t>
+    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-systems-engineer-at-commit-offshore-4455869432</t>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-moveo-source-4457448532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Tier 1 Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-tier-1-technical-support-at-gini-apps-4455720278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PointFive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior NOC Engineer | Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-noc-engineer-student-position-at-log-on-software-4458883696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist 243285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-243285-at-experis-israel-4458881880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-moveo-source-4457448532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
+    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
   </si>
   <si>
@@ -700,9 +745,6 @@
     <t xml:space="preserve">TECEZE</t>
   </si>
   <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-teceze-4458365687</t>
   </si>
   <si>
@@ -721,133 +763,121 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">remoteok</t>
@@ -975,7 +1005,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -999,7 +1029,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10">
@@ -1081,7 +1111,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1089,7 +1119,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1097,7 +1127,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1105,7 +1135,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1131,7 +1161,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
@@ -1150,7 +1180,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -1207,7 +1237,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1254,7 +1284,7 @@
         <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -1262,13 +1292,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1277,16 +1307,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1294,31 +1324,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="3">
-        <v>83</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1326,31 +1356,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3">
+        <v>84</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="3">
-        <v>61</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1358,31 +1388,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="3">
+        <v>83</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3">
-        <v>56</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1390,19 +1420,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>80</v>
@@ -1414,7 +1444,7 @@
         <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1422,31 +1452,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>61</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3">
-        <v>48</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1454,31 +1484,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="3">
+        <v>52</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="3">
-        <v>46</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -1486,31 +1516,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -1518,31 +1548,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="3">
-        <v>41</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1550,31 +1580,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>40</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="14">
@@ -1582,31 +1612,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="3">
+        <v>46</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="3">
-        <v>36</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -1614,31 +1644,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -1646,31 +1676,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="3">
+        <v>41</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>28</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="17">
@@ -1678,31 +1708,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -1710,19 +1740,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>131</v>
@@ -1734,7 +1764,7 @@
         <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -1742,31 +1772,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20">
@@ -1774,31 +1804,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -1806,31 +1836,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
@@ -1838,31 +1868,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23">
@@ -1882,7 +1912,7 @@
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>154</v>
@@ -1905,28 +1935,28 @@
         <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25">
@@ -1934,31 +1964,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26">
@@ -1966,31 +1996,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2043,7 +2073,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2058,22 +2088,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2087,7 +2117,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2096,7 +2126,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2108,7 +2138,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2131,7 +2161,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2140,21 +2170,21 @@
         <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K3" s="3">
-        <v>81</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2163,150 +2193,150 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3">
+        <v>100</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="3">
-        <v>83</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K5" s="3">
-        <v>36</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3">
+        <v>84</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3">
-        <v>61</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3">
+        <v>83</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="3">
-        <v>56</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K7" s="3">
-        <v>61</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2315,112 +2345,112 @@
         <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="K8" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>61</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3">
-        <v>48</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="K9" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="3">
+        <v>52</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="3">
-        <v>46</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="K10" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -2428,235 +2458,235 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="3">
-        <v>41</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K12" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>47</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3">
-        <v>40</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="K13" s="3">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="3">
+        <v>46</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="3">
-        <v>36</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="K14" s="3">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="K15" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="3">
+        <v>41</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>28</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="K16" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="K17" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
@@ -2665,150 +2695,150 @@
         <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="K18" s="3">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="K19" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="K20" s="3">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="K21" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="K22" s="3">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -2825,13 +2855,13 @@
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>154</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
@@ -2843,7 +2873,7 @@
         <v>156</v>
       </c>
       <c r="K23" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
@@ -2851,430 +2881,430 @@
         <v>157</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="K24" s="3">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K25" s="3">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K26" s="3">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>60</v>
+        <v>182</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="K28" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="K29" s="3">
-        <v>8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>57</v>
+        <v>163</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>192</v>
+        <v>129</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="K31" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="K32" s="3">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="K33" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>206</v>
+        <v>56</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E34" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E35" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="K35" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>57</v>
+        <v>217</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3283,22 +3313,22 @@
         <v>6</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>214</v>
+        <v>91</v>
       </c>
       <c r="K36" s="3">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -3306,66 +3336,66 @@
         <v>215</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>62</v>
+        <v>220</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>63</v>
+        <v>221</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="K37" s="3">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>219</v>
+        <v>148</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="K38" s="3">
         <v>14</v>
@@ -3373,93 +3403,95 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>225</v>
+        <v>107</v>
       </c>
       <c r="K39" s="3">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>227</v>
+        <v>130</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>228</v>
+        <v>51</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="K40" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>232</v>
+        <v>72</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>233</v>
+        <v>73</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="G41" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>32</v>
@@ -3468,47 +3500,117 @@
         <v>234</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="K41" s="3">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
+        <v>3</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="K42" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K43" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="K42" s="3">
-        <v>18</v>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K44" s="3">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K42"/>
+  <autoFilter ref="A1:K44"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3551,6 +3653,8 @@
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
     <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3558,8 +3662,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -3581,10 +3685,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3592,102 +3696,102 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>191</v>
+        <v>147</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -3696,13 +3800,13 @@
         <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3727,178 +3831,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="B2" s="3">
         <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>246</v>
+        <v>202</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>163</v>
+        <v>259</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>253</v>
+        <v>189</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B11" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3918,10 +4022,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2">
@@ -3929,10 +4033,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3">
@@ -3940,10 +4044,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
@@ -3951,10 +4055,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5">
@@ -3962,10 +4066,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6">
@@ -3976,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -3997,13 +4101,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2">
@@ -4014,7 +4118,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>237</v>
+        <v>287</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4023,22 +4127,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>237</v>
+        <v>287</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>237</v>
+        <v>287</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W36.xlsx
+++ b/reports/devops-juniors-israel-2026-W36.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-02T11:10:46</t>
+    <t xml:space="preserve">2026-09-03T11:07:06</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -100,12 +100,12 @@
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -163,483 +163,531 @@
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMIT Offshore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-systems-engineer-at-commit-offshore-4455869432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-at-paragon-4451098624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVeye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-uveye-4461013504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -652,13 +700,19 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk Technician</t>
@@ -721,7 +775,37 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-02</t>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
@@ -730,9 +814,6 @@
     <t xml:space="preserve">IBI Investment House</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
   </si>
   <si>
@@ -775,22 +856,25 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
@@ -799,15 +883,21 @@
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
@@ -820,24 +910,6 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
@@ -847,6 +919,12 @@
     <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -862,10 +940,10 @@
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1005,7 +1083,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -1013,7 +1091,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1021,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1029,7 +1107,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10">
@@ -1111,7 +1189,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -1119,7 +1197,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1127,7 +1205,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1135,7 +1213,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1161,7 +1239,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
@@ -1181,7 +1259,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="54" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1284,7 +1362,7 @@
         <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -1292,13 +1370,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1307,16 +1385,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1324,31 +1402,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1356,31 +1434,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1388,31 +1466,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1420,31 +1498,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1452,10 +1530,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>51</v>
@@ -1464,19 +1542,19 @@
         <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -1540,7 +1618,7 @@
         <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -1548,13 +1626,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
@@ -1563,16 +1641,16 @@
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -1580,10 +1658,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>51</v>
@@ -1595,16 +1673,16 @@
         <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -1612,16 +1690,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F14" s="3">
         <v>46</v>
@@ -1644,19 +1722,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>116</v>
@@ -1668,7 +1746,7 @@
         <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1676,31 +1754,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3">
+        <v>40</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="3">
-        <v>41</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -1708,31 +1786,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -1740,31 +1818,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19">
@@ -1772,31 +1850,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>137</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -1804,13 +1882,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -1819,16 +1897,16 @@
         <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21">
@@ -1836,31 +1914,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>27</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="3">
-        <v>24</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="22">
@@ -1868,13 +1946,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
@@ -1883,16 +1961,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23">
@@ -1900,31 +1978,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="3">
+        <v>24</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>23</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="24">
@@ -1932,31 +2010,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="3">
+        <v>24</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>20</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="25">
@@ -1964,31 +2042,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="26">
@@ -1996,31 +2074,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2151,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2088,22 +2166,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
@@ -2126,7 +2204,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2138,7 +2216,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2161,7 +2239,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2170,21 +2248,21 @@
         <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>13</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2193,89 +2271,89 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>82</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -2283,80 +2361,80 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>51</v>
@@ -2365,25 +2443,25 @@
         <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="K9" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2406,7 +2484,7 @@
         <v>89</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
@@ -2418,7 +2496,7 @@
         <v>91</v>
       </c>
       <c r="K10" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -2441,7 +2519,7 @@
         <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
@@ -2450,21 +2528,21 @@
         <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>25</v>
@@ -2473,30 +2551,30 @@
         <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K12" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>51</v>
@@ -2508,36 +2586,36 @@
         <v>47</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" s="3">
         <v>46</v>
@@ -2546,7 +2624,7 @@
         <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
@@ -2558,30 +2636,30 @@
         <v>113</v>
       </c>
       <c r="K14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
@@ -2590,161 +2668,161 @@
         <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="K15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="3">
+        <v>40</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="3">
-        <v>41</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="K16" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="K18" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="K19" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -2753,68 +2831,68 @@
         <v>27</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="K20" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="3">
-        <v>24</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
@@ -2823,232 +2901,232 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="K22" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="3">
+        <v>24</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>23</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="K23" s="3">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="3">
+        <v>24</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>20</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="K24" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="K25" s="3">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="K26" s="3">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="K27" s="3">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="K28" s="3">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
@@ -3062,19 +3140,19 @@
         <v>188</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>190</v>
@@ -3083,7 +3161,7 @@
         <v>191</v>
       </c>
       <c r="K29" s="3">
-        <v>56</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -3094,28 +3172,28 @@
         <v>193</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K30" s="3">
         <v>42</v>
@@ -3123,293 +3201,293 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>163</v>
+        <v>69</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="K31" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>153</v>
+        <v>203</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="K33" s="3">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>208</v>
+        <v>123</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="K34" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>44</v>
+        <v>216</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>45</v>
+        <v>167</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="K35" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>91</v>
+        <v>223</v>
       </c>
       <c r="K36" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>221</v>
+        <v>147</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E37" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K37" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>148</v>
+        <v>229</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>124</v>
+        <v>232</v>
       </c>
       <c r="K38" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>67</v>
+        <v>235</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3418,33 +3496,33 @@
         <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="K39" s="3">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3453,164 +3531,339 @@
         <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="K40" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>235</v>
+        <v>153</v>
       </c>
       <c r="K41" s="3">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>240</v>
+        <v>108</v>
       </c>
       <c r="K42" s="3">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>242</v>
+        <v>132</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>244</v>
+        <v>97</v>
       </c>
       <c r="K43" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>246</v>
+        <v>62</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>247</v>
+        <v>63</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>251</v>
+      </c>
       <c r="G44" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="K44" s="3">
-        <v>35</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K45" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="K46" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="K47" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="K48" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K49" s="3">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K44"/>
+  <autoFilter ref="A1:K49"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3655,6 +3908,11 @@
     <hyperlink ref="I42" r:id="rId41"/>
     <hyperlink ref="I43" r:id="rId42"/>
     <hyperlink ref="I44" r:id="rId43"/>
+    <hyperlink ref="I45" r:id="rId44"/>
+    <hyperlink ref="I46" r:id="rId45"/>
+    <hyperlink ref="I47" r:id="rId46"/>
+    <hyperlink ref="I48" r:id="rId47"/>
+    <hyperlink ref="I49" r:id="rId48"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3662,8 +3920,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -3685,10 +3943,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3696,127 +3954,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3">
-        <v>24</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G4"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3831,178 +4041,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>202</v>
+        <v>282</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>260</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -4022,10 +4232,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2">
@@ -4033,10 +4243,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3">
@@ -4044,10 +4254,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4">
@@ -4055,10 +4265,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5">
@@ -4066,10 +4276,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6">
@@ -4080,7 +4290,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -4101,13 +4311,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2">
@@ -4118,7 +4328,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4127,22 +4337,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W36.xlsx
+++ b/reports/devops-juniors-israel-2026-W36.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-03T11:07:06</t>
+    <t xml:space="preserve">2026-09-04T11:09:22</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,21 +91,21 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -181,201 +181,228 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMMIT Offshore</t>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-comblack-4462803997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-systems-engineer-at-commit-offshore-4455869432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-at-paragon-4451098624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVeye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-uveye-4461013504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PointFive</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -385,6 +412,21 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
@@ -421,18 +463,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Field Support Engineer</t>
   </si>
   <si>
@@ -451,6 +481,15 @@
     <t xml:space="preserve">2026-08-27</t>
   </si>
   <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -466,246 +505,132 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -715,57 +640,6 @@
     <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-moveo-source-4457448532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Tier 1 Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-tier-1-technical-support-at-gini-apps-4455720278</t>
-  </si>
-  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -775,100 +649,85 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TECEZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-teceze-4458365687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
@@ -877,39 +736,12 @@
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
@@ -931,19 +763,19 @@
     <t xml:space="preserve">Pivot path advice</t>
   </si>
   <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1083,7 +915,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -1091,7 +923,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +931,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +939,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="10">
@@ -1189,7 +1021,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1197,7 +1029,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1213,7 +1045,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1239,7 +1071,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
@@ -1247,7 +1079,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1315,7 +1147,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1347,7 +1179,7 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1382,13 +1214,13 @@
         <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>59</v>
@@ -1411,16 +1243,16 @@
         <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>65</v>
@@ -1443,16 +1275,16 @@
         <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>71</v>
@@ -1475,7 +1307,7 @@
         <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3">
         <v>61</v>
@@ -1504,25 +1336,25 @@
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
         <v>56</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -1530,19 +1362,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>85</v>
@@ -1554,7 +1386,7 @@
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1562,31 +1394,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
         <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1594,31 +1426,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
         <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -1626,31 +1458,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1658,31 +1490,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F13" s="3">
         <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
@@ -1690,31 +1522,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="3">
         <v>46</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -1722,31 +1554,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -1754,31 +1586,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17">
@@ -1786,31 +1618,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
@@ -1818,31 +1650,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -1850,31 +1682,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -1882,31 +1714,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21">
@@ -1914,31 +1746,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -1946,31 +1778,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -1978,31 +1810,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
         <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24">
@@ -2010,31 +1842,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
         <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25">
@@ -2042,31 +1874,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
         <v>23</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26">
@@ -2074,31 +1906,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2137,7 +1969,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2151,7 +1983,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2166,22 +1998,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2195,7 +2027,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2204,7 +2036,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2216,7 +2048,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2230,7 +2062,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2239,7 +2071,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2251,7 +2083,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -2268,16 +2100,16 @@
         <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>59</v>
@@ -2286,7 +2118,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -2300,19 +2132,19 @@
         <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>65</v>
@@ -2321,7 +2153,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2335,19 +2167,19 @@
         <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>71</v>
@@ -2370,7 +2202,7 @@
         <v>51</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
         <v>61</v>
@@ -2379,7 +2211,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2391,7 +2223,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2402,54 +2234,54 @@
         <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
         <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="K8" s="3">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2458,873 +2290,873 @@
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3">
         <v>52</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K10" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
         <v>48</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
         <v>47</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K13" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" s="3">
         <v>46</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E16" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K16" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K17" s="3">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K18" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="K19" s="3">
-        <v>14</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="K20" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="K21" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E22" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="K22" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
         <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="K23" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
         <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="K24" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
         <v>23</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K25" s="3">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K26" s="3">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="3">
+        <v>13</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>20</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="K27" s="3">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="K28" s="3">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K29" s="3">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E30" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="K30" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="K31" s="3">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K32" s="3">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>56</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>156</v>
+        <v>57</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>209</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>210</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>211</v>
+        <v>87</v>
       </c>
       <c r="K33" s="3">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>123</v>
+        <v>211</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>212</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E34" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>213</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
@@ -3333,10 +3165,10 @@
         <v>214</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K34" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -3347,523 +3179,33 @@
         <v>216</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>12</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>217</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="K35" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="3">
-        <v>10</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="K36" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="3">
-        <v>9</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="K37" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="3">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="K38" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="3">
-        <v>6</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K39" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="3">
-        <v>6</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K40" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="3">
-        <v>6</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K41" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="3">
-        <v>6</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K42" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="3">
-        <v>6</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="3">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K44" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K45" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E46" s="3">
-        <v>3</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="K46" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="3">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="K47" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" s="3">
-        <v>3</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="K48" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K49" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K49"/>
+  <autoFilter ref="A1:K35"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3899,20 +3241,6 @@
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
-    <hyperlink ref="I37" r:id="rId36"/>
-    <hyperlink ref="I38" r:id="rId37"/>
-    <hyperlink ref="I39" r:id="rId38"/>
-    <hyperlink ref="I40" r:id="rId39"/>
-    <hyperlink ref="I41" r:id="rId40"/>
-    <hyperlink ref="I42" r:id="rId41"/>
-    <hyperlink ref="I43" r:id="rId42"/>
-    <hyperlink ref="I44" r:id="rId43"/>
-    <hyperlink ref="I45" r:id="rId44"/>
-    <hyperlink ref="I46" r:id="rId45"/>
-    <hyperlink ref="I47" r:id="rId46"/>
-    <hyperlink ref="I48" r:id="rId47"/>
-    <hyperlink ref="I49" r:id="rId48"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3920,9 +3248,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3943,10 +3271,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3960,10 +3288,10 @@
         <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>70</v>
@@ -3977,56 +3305,32 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3">
-        <v>40</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4041,178 +3345,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>277</v>
+        <v>220</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>278</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>280</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>281</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>282</v>
+        <v>225</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>283</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>284</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>285</v>
+        <v>229</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>287</v>
+        <v>182</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>288</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>291</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>292</v>
+        <v>236</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>293</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>294</v>
+        <v>238</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>298</v>
+        <v>242</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>291</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>301</v>
+        <v>245</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -4232,10 +3536,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>304</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2">
@@ -4243,10 +3547,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>305</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3">
@@ -4254,10 +3558,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>306</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
@@ -4268,7 +3572,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>307</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
@@ -4276,10 +3580,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>308</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6">
@@ -4290,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>309</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -4311,13 +3615,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>310</v>
+        <v>254</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>312</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -4325,10 +3629,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>313</v>
+        <v>257</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4337,22 +3641,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>313</v>
+        <v>257</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>313</v>
+        <v>257</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W36.xlsx
+++ b/reports/devops-juniors-israel-2026-W36.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04T11:09:22</t>
+    <t xml:space="preserve">2026-09-06T10:49:27</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,12 +94,12 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -163,15 +163,27 @@
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Paragon</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -181,6 +193,24 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Devops Student</t>
   </si>
   <si>
@@ -199,510 +229,432 @@
     <t xml:space="preserve">2026-07-27</t>
   </si>
   <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-comblack-4462803997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux/Windows System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webox LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-windows-system-administrator-at-webox-ltd-4461811690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVeye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-uveye-4464029135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4459914959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PointFive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
@@ -712,49 +664,52 @@
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -766,10 +721,10 @@
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
@@ -915,7 +870,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -923,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -931,7 +886,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -939,7 +894,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10">
@@ -1021,7 +976,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -1029,7 +984,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1037,7 +992,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1045,7 +1000,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1071,7 +1026,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -1147,7 +1102,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1194,7 +1149,7 @@
         <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -1202,31 +1157,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="3">
-        <v>83</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1234,31 +1189,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1266,31 +1221,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="3">
+        <v>83</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="3">
-        <v>68</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -1298,31 +1253,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1330,31 +1285,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -1368,25 +1323,25 @@
         <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>61</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>56</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1394,19 +1349,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>90</v>
@@ -1418,7 +1373,7 @@
         <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -1426,31 +1381,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="3">
+        <v>47</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="3">
-        <v>48</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -1458,31 +1413,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>48</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1490,31 +1445,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
         <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="14">
@@ -1522,13 +1477,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>29</v>
@@ -1554,7 +1509,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>115</v>
@@ -1595,10 +1550,10 @@
         <v>122</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>123</v>
@@ -1610,7 +1565,7 @@
         <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17">
@@ -1618,31 +1573,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18">
@@ -1650,31 +1605,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3">
+        <v>41</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="3">
-        <v>39</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -1682,31 +1637,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20">
@@ -1714,13 +1669,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -1729,16 +1684,16 @@
         <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -1746,10 +1701,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>51</v>
@@ -1761,13 +1716,13 @@
         <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>48</v>
@@ -1778,31 +1733,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
         <v>27</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23">
@@ -1810,13 +1765,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1825,16 +1780,16 @@
         <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24">
@@ -1842,13 +1797,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
@@ -1857,16 +1812,16 @@
         <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25">
@@ -1874,31 +1829,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26">
@@ -1906,31 +1861,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="3">
+        <v>23</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="3">
-        <v>17</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1983,7 +1938,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -1998,22 +1953,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2">
@@ -2027,7 +1982,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2036,7 +1991,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2048,7 +2003,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2071,7 +2026,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2080,185 +2035,185 @@
         <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K3" s="3">
-        <v>84</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3">
+        <v>100</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="3">
-        <v>83</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K4" s="3">
-        <v>39</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3">
+        <v>83</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3">
-        <v>68</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K7" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2269,54 +2224,54 @@
         <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3">
+        <v>61</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>56</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="K9" s="3">
-        <v>64</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
@@ -2325,126 +2280,126 @@
         <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="K10" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3">
+        <v>47</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3">
-        <v>48</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="K11" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="3">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>48</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K12" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
         <v>47</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="K13" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>29</v>
@@ -2456,7 +2411,7 @@
         <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
@@ -2468,12 +2423,12 @@
         <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>115</v>
@@ -2491,7 +2446,7 @@
         <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
@@ -2503,7 +2458,7 @@
         <v>119</v>
       </c>
       <c r="K15" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -2517,16 +2472,16 @@
         <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
@@ -2535,126 +2490,126 @@
         <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="K16" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="K17" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3">
+        <v>41</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="3">
-        <v>39</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K18" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="K19" s="3">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -2663,30 +2618,30 @@
         <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="K20" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>51</v>
@@ -2698,68 +2653,68 @@
         <v>28</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K21" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
         <v>27</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="K22" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2768,33 +2723,33 @@
         <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="K23" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
@@ -2803,208 +2758,208 @@
         <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="K24" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
+        <v>24</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K25" s="3">
         <v>23</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K25" s="3">
-        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="3">
+        <v>23</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="3">
-        <v>17</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="K26" s="3">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="K27" s="3">
-        <v>58</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="K28" s="3">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
         <v>10</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="K29" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>28</v>
@@ -3013,199 +2968,94 @@
         <v>9</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>114</v>
       </c>
       <c r="K30" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="K31" s="3">
-        <v>9</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>205</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>207</v>
+        <v>108</v>
       </c>
       <c r="K32" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="3">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="K33" s="3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E34" s="3">
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="K34" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="K35" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K35"/>
+  <autoFilter ref="A1:K32"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3238,9 +3088,6 @@
     <hyperlink ref="I30" r:id="rId29"/>
     <hyperlink ref="I31" r:id="rId30"/>
     <hyperlink ref="I32" r:id="rId31"/>
-    <hyperlink ref="I33" r:id="rId32"/>
-    <hyperlink ref="I34" r:id="rId33"/>
-    <hyperlink ref="I35" r:id="rId34"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3248,9 +3095,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3271,10 +3118,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3282,55 +3129,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>44</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3">
+        <v>40</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3345,178 +3264,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="B3" s="3">
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -3536,10 +3455,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2">
@@ -3547,10 +3466,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">
@@ -3558,10 +3477,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4">
@@ -3569,10 +3488,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5">
@@ -3580,10 +3499,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6">
@@ -3594,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3615,13 +3534,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2">
@@ -3632,7 +3551,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3641,22 +3560,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="D4" s="3"/>
     </row>
